--- a/public/cba_pista/src/Other/Notas.xlsx
+++ b/public/cba_pista/src/Other/Notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\manuel-t\public\cba_pista\src\Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17725AEC-4742-40DC-8871-79AB5CC96863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D0E361-420D-4A10-AF15-E365C7C7E32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Circuits_calendar</t>
   </si>
@@ -88,19 +88,61 @@
   </si>
   <si>
     <t>locked_at</t>
+  </si>
+  <si>
+    <t>user_activity</t>
+  </si>
+  <si>
+    <t>id_activity</t>
+  </si>
+  <si>
+    <t>id_user</t>
+  </si>
+  <si>
+    <t>activity</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>detail</t>
+  </si>
+  <si>
+    <t>- Delete</t>
+  </si>
+  <si>
+    <t>- Edit</t>
+  </si>
+  <si>
+    <t>- End Run</t>
+  </si>
+  <si>
+    <t>- Log In</t>
+  </si>
+  <si>
+    <t>- Log Out</t>
+  </si>
+  <si>
+    <t>- Start Run</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -117,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -164,16 +206,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:H14"/>
+  <dimension ref="D3:T14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.88671875" style="1"/>
@@ -463,11 +598,14 @@
     <col min="6" max="6" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="1"/>
     <col min="8" max="8" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D4" s="4" t="s">
         <v>0</v>
       </c>
@@ -477,8 +615,15 @@
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="O4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="T4" s="5"/>
+    </row>
+    <row r="5" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D5" s="2" t="s">
         <v>1</v>
       </c>
@@ -488,8 +633,14 @@
       <c r="H5" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="Q5" s="5"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
@@ -499,8 +650,12 @@
       <c r="H6" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
@@ -510,8 +665,14 @@
       <c r="H7" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -521,44 +682,73 @@
       <c r="H8" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J8" s="13"/>
+      <c r="K8" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="4:20" x14ac:dyDescent="0.3">
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J9" s="13"/>
+      <c r="K9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J10" s="13"/>
+      <c r="K10" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="4:20" x14ac:dyDescent="0.3">
       <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J11" s="13"/>
+      <c r="K11" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="4:20" x14ac:dyDescent="0.3">
       <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="J12" s="13"/>
+      <c r="K12" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="4:20" x14ac:dyDescent="0.3">
       <c r="F13" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="4:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="4:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F14" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="J14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>